--- a/backend/watch/PRECOS IFAL JULHO.xlsx
+++ b/backend/watch/PRECOS IFAL JULHO.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\AppData\Local\Temp\Rar$DIa13844.23017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.0.0.20\Compras\1.COMPRAS\PRECOS SUBIDOS SIRIUS\FALTA SUBIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F8838A-80DE-427C-B9F8-62D9E0A9FE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{869A031B-0DC2-4A8A-9317-08D150506EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-4725" windowWidth="38640" windowHeight="15840" xr2:uid="{32453748-1038-4035-9290-C8F3DD52DB69}"/>
+    <workbookView xWindow="-38400" yWindow="-4605" windowWidth="19200" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,38 +37,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>CODIGO DE BARRAS EAN 13</t>
+    <t>CODIGO BARRAS</t>
   </si>
   <si>
-    <t>PRECO</t>
+    <t>PF</t>
   </si>
   <si>
-    <t>FILIAL (PR, MT, SC, MS)</t>
+    <t>DESCONTO</t>
   </si>
   <si>
-    <t>NOME LABORATORIO</t>
+    <t>PREÇO FINAL</t>
   </si>
   <si>
-    <t>DATA VALIDADE</t>
+    <t>EMPRESA</t>
   </si>
   <si>
-    <t>todas</t>
+    <t>COD GLOBAL LAB</t>
   </si>
   <si>
-    <t>Ifal</t>
+    <t>data validade</t>
   </si>
   <si>
-    <t>ifal</t>
+    <t>REPASSE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _R_$_-;\-* #,##0.00\ _R_$_-;_-* &quot;-&quot;??\ _R_$_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -86,11 +88,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,21 +110,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+  <cellStyles count="5">
+    <cellStyle name="Moeda" xfId="4" builtinId="4"/>
+    <cellStyle name="Moeda 2" xfId="1" xr:uid="{DCAD208E-EF1B-4E8E-87A7-D12806BB3300}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Vírgula 2" xfId="2" xr:uid="{37B938A5-9F12-4243-8FE6-2AEDB58A02CC}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -156,7 +162,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -168,7 +174,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -215,23 +221,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -267,23 +256,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -435,286 +407,1000 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D25F2D-4D58-49A5-BFF9-419C75286C07}">
-  <dimension ref="A1:E56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Planilha1"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>7898016410042</v>
       </c>
-      <c r="B2" s="2">
+      <c r="E2" s="4"/>
+      <c r="F2" s="5">
         <v>8.1199999999999992</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>71</v>
+      </c>
+      <c r="L2" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>7898016410158</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5">
+        <v>5.48</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>71</v>
+      </c>
+      <c r="L3" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>7898016410295</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>71</v>
+      </c>
+      <c r="L4" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>7898016410493</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>71</v>
+      </c>
+      <c r="L5" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>7898016410752</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>71</v>
+      </c>
+      <c r="L6" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>789801641916</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>71</v>
+      </c>
+      <c r="L7" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7898016410196</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5">
+        <v>48.51</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>71</v>
+      </c>
+      <c r="L8" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7898016410042</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>71</v>
+      </c>
+      <c r="L9" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7898016410158</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5">
+        <v>5.48</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>71</v>
+      </c>
+      <c r="L10" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7898016410295</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>71</v>
+      </c>
+      <c r="L11" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>7898016410493</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>71</v>
+      </c>
+      <c r="L12" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>7898016410752</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>71</v>
+      </c>
+      <c r="L13" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>789801641916</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>71</v>
+      </c>
+      <c r="L14" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>7898016410196</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5">
+        <v>48.51</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>71</v>
+      </c>
+      <c r="L15" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>7898016410042</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>71</v>
+      </c>
+      <c r="L16" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>7898016410158</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5">
+        <v>5.48</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>71</v>
+      </c>
+      <c r="L17" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>7898016410295</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>71</v>
+      </c>
+      <c r="L18" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>7898016410493</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>71</v>
+      </c>
+      <c r="L19" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>7898016410752</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>71</v>
+      </c>
+      <c r="L20" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>789801641916</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>71</v>
+      </c>
+      <c r="L21" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7898016410196</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5">
+        <v>48.51</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>71</v>
+      </c>
+      <c r="L22" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>7898016410042</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G23">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H23">
+        <v>71</v>
+      </c>
+      <c r="L23" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7898016410158</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5">
+        <v>5.48</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <v>71</v>
+      </c>
+      <c r="L24" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>7898016410295</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5">
+        <v>35.909999999999997</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>71</v>
+      </c>
+      <c r="L25" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>7898016410493</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="5">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>71</v>
+      </c>
+      <c r="L26" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>7898016410752</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27">
+        <v>71</v>
+      </c>
+      <c r="L27" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>789801641916</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28">
+        <v>71</v>
+      </c>
+      <c r="L28" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>7898016410196</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5">
+        <v>48.51</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <v>71</v>
+      </c>
+      <c r="L29" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>7898016410042</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="G30">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="H30">
+        <v>71</v>
+      </c>
+      <c r="L30" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>7898016410158</v>
       </c>
-      <c r="B3" s="2">
+      <c r="E31" s="4"/>
+      <c r="F31" s="5">
         <v>5.48</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="G31">
+        <v>6</v>
+      </c>
+      <c r="H31">
+        <v>71</v>
+      </c>
+      <c r="L31" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>7898016410295</v>
       </c>
-      <c r="B4" s="2">
+      <c r="E32" s="4"/>
+      <c r="F32" s="5">
         <v>35.909999999999997</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>71</v>
+      </c>
+      <c r="L32" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>7898016410493</v>
       </c>
-      <c r="B5" s="2">
+      <c r="E33" s="4"/>
+      <c r="F33" s="5">
         <v>81.900000000000006</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="G33">
+        <v>6</v>
+      </c>
+      <c r="H33">
+        <v>71</v>
+      </c>
+      <c r="L33" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>7898016410752</v>
       </c>
-      <c r="B6" s="2">
+      <c r="E34" s="4"/>
+      <c r="F34" s="5">
         <v>5.8</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
+        <v>71</v>
+      </c>
+      <c r="L34" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>789801641916</v>
       </c>
-      <c r="B7" s="2">
+      <c r="E35" s="4"/>
+      <c r="F35" s="5">
         <v>8.8800000000000008</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35">
+        <v>71</v>
+      </c>
+      <c r="L35" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>7898016410196</v>
       </c>
-      <c r="B8" s="4">
+      <c r="E36" s="4"/>
+      <c r="F36" s="5">
         <v>48.51</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="3"/>
+      <c r="G36">
+        <v>6</v>
+      </c>
+      <c r="H36">
+        <v>71</v>
+      </c>
+      <c r="L36" s="3">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E37" s="4"/>
+      <c r="L37" s="3"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E38" s="4"/>
+      <c r="L38" s="3"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E39" s="4"/>
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E40" s="4"/>
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E41" s="4"/>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E42" s="4"/>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E43" s="4"/>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E44" s="4"/>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E45" s="4"/>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E46" s="4"/>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E47" s="4"/>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E48" s="4"/>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E49" s="4"/>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E50" s="4"/>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E51" s="4"/>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E52" s="4"/>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E53" s="4"/>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E54" s="4"/>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E55" s="4"/>
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E56" s="4"/>
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E57" s="4"/>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E58" s="4"/>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E59" s="4"/>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E60" s="4"/>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E61" s="4"/>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E62" s="4"/>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E63" s="4"/>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E64" s="4"/>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E65" s="4"/>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E66" s="4"/>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E67" s="4"/>
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E68" s="4"/>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E69" s="4"/>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E70" s="4"/>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E71" s="4"/>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E72" s="4"/>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E73" s="4"/>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E74" s="4"/>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E75" s="4"/>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E76" s="4"/>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E77" s="4"/>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="78" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E78" s="4"/>
+      <c r="L78" s="3"/>
+    </row>
+    <row r="79" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E79" s="4"/>
+      <c r="L79" s="3"/>
+    </row>
+    <row r="80" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E80" s="4"/>
+      <c r="L80" s="3"/>
+    </row>
+    <row r="81" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E81" s="4"/>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E82" s="4"/>
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E83" s="4"/>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E84" s="4"/>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E85" s="4"/>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E86" s="4"/>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E87" s="4"/>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E88" s="4"/>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E89" s="4"/>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E90" s="4"/>
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E91" s="4"/>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E92" s="4"/>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E93" s="4"/>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E94" s="4"/>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E95" s="4"/>
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E96" s="4"/>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E97" s="4"/>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E98" s="4"/>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E99" s="4"/>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E100" s="4"/>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E101" s="4"/>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E102" s="4"/>
+      <c r="L102" s="3"/>
+    </row>
+    <row r="103" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E103" s="4"/>
+      <c r="L103" s="3"/>
+    </row>
+    <row r="104" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E104" s="4"/>
+      <c r="L104" s="3"/>
+    </row>
+    <row r="105" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E105" s="4"/>
+      <c r="L105" s="3"/>
+    </row>
+    <row r="106" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E106" s="4"/>
+      <c r="L106" s="3"/>
+    </row>
+    <row r="107" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E107" s="4"/>
+      <c r="L107" s="3"/>
+    </row>
+    <row r="108" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E108" s="4"/>
+      <c r="L108" s="3"/>
+    </row>
+    <row r="109" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E109" s="4"/>
+      <c r="L109" s="3"/>
+    </row>
+    <row r="110" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E110" s="4"/>
+      <c r="L110" s="3"/>
+    </row>
+    <row r="111" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E111" s="4"/>
+      <c r="L111" s="3"/>
+    </row>
+    <row r="112" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E112" s="4"/>
+      <c r="L112" s="3"/>
+    </row>
+    <row r="113" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E113" s="4"/>
+      <c r="L113" s="3"/>
+    </row>
+    <row r="114" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E114" s="4"/>
+      <c r="L114" s="3"/>
+    </row>
+    <row r="115" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E115" s="4"/>
+      <c r="L115" s="3"/>
+    </row>
+    <row r="116" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E116" s="4"/>
+      <c r="L116" s="3"/>
+    </row>
+    <row r="117" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E117" s="4"/>
+      <c r="L117" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E56" xr:uid="{C8D25F2D-4D58-49A5-BFF9-419C75286C07}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>